--- a/DateBase/orders/Nha Thu_2026-4-7.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-7.xlsx
@@ -1246,6 +1246,9 @@
       <c r="G2" t="str">
         <v>0101055520205551555515110771055105105510551022355855555101510355151051055555101055551030302020561010401520105151515101055101051010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
